--- a/兆妤/112~114年花蓮縣公路客運定期票分析/112~114年花蓮縣公路客運定期票.xlsx
+++ b/兆妤/112~114年花蓮縣公路客運定期票分析/112~114年花蓮縣公路客運定期票.xlsx
@@ -1,62 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\115_Midterm-Report\兆妤\112~114年花蓮縣公路客運定期票分析\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD5ACB2D-B28D-4DA0-A249-8E8550DB961F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="人數表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="比例表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="人數表" sheetId="1" r:id="rId1"/>
+    <sheet name="比例表" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">非定期票</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花蓮縣199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">花蓮縣399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">台東縣299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">總運量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>非定期票</t>
+  </si>
+  <si>
+    <t>花蓮縣199</t>
+  </si>
+  <si>
+    <t>花蓮縣399</t>
+  </si>
+  <si>
+    <t>台東縣299</t>
+  </si>
+  <si>
+    <t>總運量</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <r>
+      <t>113</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>114</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>年成長率</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="176" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="#,##0_ "/>
+  </numFmts>
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,16 +150,37 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="百分比" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -367,11 +462,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -384,89 +482,217 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
+      <c r="E1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2">
+        <v>8197</v>
+      </c>
+      <c r="C2" s="2">
+        <v>60051</v>
+      </c>
+      <c r="D2" s="2">
+        <v>55705</v>
+      </c>
+      <c r="E2" s="4">
+        <f>(C2-B2)/B2</f>
+        <v>6.3259729169208248</v>
+      </c>
+      <c r="F2" s="4">
+        <f>(D2-C2)/C2</f>
+        <v>-7.2371817288637993E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1">
+        <v>2.0252808017117398E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.13319684857733499</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.154711615105386</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>2.7773380325892799E-6</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2">
+        <v>6012</v>
+      </c>
+      <c r="C6" s="2">
+        <v>14674</v>
+      </c>
+      <c r="D6" s="2">
+        <v>13297</v>
+      </c>
+      <c r="E6" s="4">
+        <f>(C6-B6)/B6</f>
+        <v>1.4407850964737192</v>
+      </c>
+      <c r="F6" s="4">
+        <f>(D6-C6)/C6</f>
+        <v>-9.3839443914406434E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1">
+        <v>1.48542005366488E-2</v>
+      </c>
+      <c r="C7" s="1">
+        <v>3.2547843600003498E-2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3.6930263819339698E-2</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B8" s="2">
         <v>390525</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C8" s="2">
         <v>376119</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D8" s="2">
         <v>291054</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="n">
-        <v>8197</v>
-      </c>
-      <c r="C4" t="n">
-        <v>60051</v>
-      </c>
-      <c r="D4" t="n">
-        <v>55705</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6012</v>
-      </c>
-      <c r="C5" t="n">
-        <v>14674</v>
-      </c>
-      <c r="D5" t="n">
-        <v>13297</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
+      <c r="E8" s="4">
+        <f>(C8-B8)/B8</f>
+        <v>-3.6888803533704627E-2</v>
+      </c>
+      <c r="F8" s="4">
+        <f>(D8-C8)/C8</f>
+        <v>-0.22616512327215588</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
+        <v>0.96489299144623397</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0.834255307822662</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.80835534373724205</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B10" s="2">
         <v>404734</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C10" s="2">
         <v>450844</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D10" s="2">
         <v>360057</v>
       </c>
+      <c r="E10" s="4">
+        <f t="shared" ref="E6:E10" si="0">(C10-B10)/B10</f>
+        <v>0.11392667776860851</v>
+      </c>
+      <c r="F10" s="4">
+        <f t="shared" ref="F6:F10" si="1">(D10-C10)/C10</f>
+        <v>-0.20137120600473779</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>1</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="A4:A5"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -480,78 +706,79 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.964892991446234</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2" s="1">
+        <v>0.96489299144623397</v>
+      </c>
+      <c r="C2" s="1">
         <v>0.834255307822662</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.808355343737242</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="D2" s="1">
+        <v>0.80835534373724205</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="1">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.00000277733803258928</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="D3" s="1">
+        <v>2.7773380325892799E-6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.0202528080171174</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.133196848577335</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4" s="1">
+        <v>2.0252808017117398E-2</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0.13319684857733499</v>
+      </c>
+      <c r="D4" s="1">
         <v>0.154711615105386</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.0148542005366488</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0325478436000035</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.0369302638193397</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5" s="1">
+        <v>1.48542005366488E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3.2547843600003498E-2</v>
+      </c>
+      <c r="D5" s="1">
+        <v>3.6930263819339698E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>